--- a/exports/trend_1d/GLENMARK_full_report.xlsx
+++ b/exports/trend_1d/GLENMARK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.15</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42089</v>
+        <v>42090</v>
       </c>
       <c r="H2" t="n">
-        <v>792.4</v>
+        <v>771.75</v>
       </c>
       <c r="I2" t="n">
         <v>774.1350340181471</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>10.84</v>
+        <v>7.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.51</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>12.49</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42101</v>
+        <v>42102</v>
       </c>
       <c r="H3" t="n">
-        <v>844.2</v>
+        <v>881.75</v>
       </c>
       <c r="I3" t="n">
         <v>867.337909336615</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.390000000000001</v>
+        <v>-14.25</v>
       </c>
       <c r="L3" t="n">
-        <v>11.84</v>
+        <v>16.79</v>
       </c>
       <c r="M3" t="n">
-        <v>1.46</v>
+        <v>4.16</v>
       </c>
       <c r="N3" t="n">
         <v>7.38</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.24</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42212</v>
+        <v>42213</v>
       </c>
       <c r="H4" t="n">
-        <v>1036.4</v>
+        <v>991.15</v>
       </c>
       <c r="I4" t="n">
         <v>1014.604596402296</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K4" t="n">
-        <v>17.54</v>
+        <v>12.41</v>
       </c>
       <c r="L4" t="n">
         <v>8.48</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42226</v>
+        <v>42227</v>
       </c>
       <c r="H5" t="n">
-        <v>1052.45</v>
+        <v>1059.84</v>
       </c>
       <c r="I5" t="n">
         <v>1057.131488546528</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.18</v>
+        <v>-6.93</v>
       </c>
       <c r="L5" t="n">
-        <v>7.34</v>
+        <v>7.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.42</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42248</v>
+        <v>42249</v>
       </c>
       <c r="H6" t="n">
-        <v>1124.5</v>
+        <v>1079.55</v>
       </c>
       <c r="I6" t="n">
         <v>1082.733465868103</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>6.1</v>
+        <v>1.86</v>
       </c>
       <c r="L6" t="n">
         <v>3.1</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>19.63</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42359</v>
+        <v>42360</v>
       </c>
       <c r="H7" t="n">
-        <v>929.25</v>
+        <v>938.1</v>
       </c>
       <c r="I7" t="n">
         <v>938.0516357363086</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K7" t="n">
-        <v>13.92</v>
+        <v>13.1</v>
       </c>
       <c r="L7" t="n">
         <v>5.01</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>906.95</v>
+        <v>866.25</v>
       </c>
       <c r="I8" t="n">
         <v>875.1172721696613</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.32</v>
+        <v>-7.66</v>
       </c>
       <c r="L8" t="n">
-        <v>3.9</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.53</v>
+        <v>1.32</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>4.49</v>
       </c>
       <c r="O8" t="n">
         <v>0.95</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.56</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>792.7</v>
+        <v>812.2</v>
       </c>
       <c r="I9" t="n">
         <v>796.1799869167384</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K9" t="n">
-        <v>8.49</v>
+        <v>6.24</v>
       </c>
       <c r="L9" t="n">
         <v>3.77</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.64</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42523</v>
+        <v>42524</v>
       </c>
       <c r="H10" t="n">
-        <v>834.65</v>
+        <v>809.95</v>
       </c>
       <c r="I10" t="n">
         <v>823.6373111472734</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" t="n">
-        <v>2.76</v>
+        <v>-0.28</v>
       </c>
       <c r="L10" t="n">
         <v>6.6</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42552</v>
+        <v>42555</v>
       </c>
       <c r="H11" t="n">
-        <v>801.15</v>
+        <v>820.15</v>
       </c>
       <c r="I11" t="n">
         <v>813.5426946984029</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>1.09</v>
+        <v>-1.26</v>
       </c>
       <c r="L11" t="n">
         <v>3.73</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="O11" t="n">
         <v>-2.96</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.58</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H12" t="n">
-        <v>912.55</v>
+        <v>869.15</v>
       </c>
       <c r="I12" t="n">
         <v>875.6633984563108</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K12" t="n">
-        <v>11.27</v>
+        <v>5.97</v>
       </c>
       <c r="L12" t="n">
         <v>1.48</v>
@@ -1125,7 +1268,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="O12" t="n">
         <v>2.37</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>13.36</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42768</v>
+        <v>42769</v>
       </c>
       <c r="H13" t="n">
-        <v>909.05</v>
+        <v>947.3</v>
       </c>
       <c r="I13" t="n">
         <v>923.6291843274031</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.59</v>
+        <v>-8.99</v>
       </c>
       <c r="L13" t="n">
-        <v>9.869999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>6.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.22</v>
+        <v>4.21</v>
       </c>
       <c r="O13" t="n">
         <v>-4.76</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>7.15</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42802</v>
+        <v>42803</v>
       </c>
       <c r="H14" t="n">
-        <v>893.85</v>
+        <v>885.7</v>
       </c>
       <c r="I14" t="n">
         <v>888.882571947757</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.64</v>
+        <v>-6.5</v>
       </c>
       <c r="L14" t="n">
-        <v>5.92</v>
+        <v>6.77</v>
       </c>
       <c r="M14" t="n">
         <v>1.66</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.72</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42923</v>
+        <v>42926</v>
       </c>
       <c r="H15" t="n">
-        <v>665.25</v>
+        <v>677.3</v>
       </c>
       <c r="I15" t="n">
         <v>665.4763246273175</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K15" t="n">
-        <v>24.89</v>
+        <v>23.53</v>
       </c>
       <c r="L15" t="n">
         <v>4.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.12</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42954</v>
+        <v>42955</v>
       </c>
       <c r="H16" t="n">
-        <v>688.75</v>
+        <v>668.25</v>
       </c>
       <c r="I16" t="n">
         <v>684.4234837825611</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>1.69</v>
+        <v>-1.34</v>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="M16" t="n">
         <v>0.83</v>
       </c>
       <c r="N16" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
         <v>1.81</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42998</v>
+        <v>42999</v>
       </c>
       <c r="H17" t="n">
-        <v>610.2</v>
+        <v>628.7</v>
       </c>
       <c r="I17" t="n">
         <v>624.7031907302855</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>8.69</v>
+        <v>5.92</v>
       </c>
       <c r="L17" t="n">
         <v>3.85</v>
@@ -1410,7 +1613,7 @@
         <v>1.7</v>
       </c>
       <c r="N17" t="n">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
         <v>-2.98</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43047</v>
+        <v>43048</v>
       </c>
       <c r="H18" t="n">
-        <v>597.35</v>
+        <v>592.05</v>
       </c>
       <c r="I18" t="n">
         <v>596.4555231040819</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.99</v>
+        <v>-5.83</v>
       </c>
       <c r="L18" t="n">
-        <v>5.92</v>
+        <v>7.29</v>
       </c>
       <c r="M18" t="n">
         <v>0.57</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43090</v>
+        <v>43091</v>
       </c>
       <c r="H19" t="n">
-        <v>562.95</v>
+        <v>567.6</v>
       </c>
       <c r="I19" t="n">
         <v>566.6385255374367</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K19" t="n">
-        <v>4.92</v>
+        <v>4.13</v>
       </c>
       <c r="L19" t="n">
         <v>1.68</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43131</v>
+        <v>43132</v>
       </c>
       <c r="H20" t="n">
-        <v>606.2</v>
+        <v>588.15</v>
       </c>
       <c r="I20" t="n">
         <v>596.8821737776034</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>6.8</v>
+        <v>3.62</v>
       </c>
       <c r="L20" t="n">
         <v>1.3</v>
@@ -1581,7 +1820,7 @@
         <v>0.84</v>
       </c>
       <c r="N20" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="O20" t="n">
         <v>0.83</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.48</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43202</v>
+        <v>43203</v>
       </c>
       <c r="H21" t="n">
-        <v>558.3</v>
+        <v>582.05</v>
       </c>
       <c r="I21" t="n">
         <v>568.9598094608588</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K21" t="n">
-        <v>5.08</v>
+        <v>1.04</v>
       </c>
       <c r="L21" t="n">
         <v>3.55</v>
@@ -1638,7 +1889,7 @@
         <v>1.26</v>
       </c>
       <c r="N21" t="n">
-        <v>4.02</v>
+        <v>4.25</v>
       </c>
       <c r="O21" t="n">
         <v>-2.98</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>10.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43223</v>
+        <v>43224</v>
       </c>
       <c r="H22" t="n">
-        <v>542.5</v>
+        <v>535.3</v>
       </c>
       <c r="I22" t="n">
         <v>537.4442857628671</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.79</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>7.68</v>
+        <v>8.26</v>
       </c>
       <c r="M22" t="n">
-        <v>0.21</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>3.85</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>9.42</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43258</v>
+        <v>43259</v>
       </c>
       <c r="H23" t="n">
-        <v>536.65</v>
+        <v>556.75</v>
       </c>
       <c r="I23" t="n">
         <v>549.9686751040143</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.25</v>
+        <v>-4.01</v>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>4.61</v>
       </c>
       <c r="M23" t="n">
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>-1.33</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H24" t="n">
-        <v>654.8</v>
+        <v>629.8</v>
       </c>
       <c r="I24" t="n">
         <v>635.9168178302679</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K24" t="n">
-        <v>17.61</v>
+        <v>13.12</v>
       </c>
       <c r="L24" t="n">
         <v>3.68</v>
@@ -1809,7 +2096,7 @@
         <v>2.71</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>3.82</v>
       </c>
       <c r="O24" t="n">
         <v>3.75</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>13.87</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43410</v>
+        <v>43413</v>
       </c>
       <c r="H25" t="n">
-        <v>657.5</v>
+        <v>676.15</v>
       </c>
       <c r="I25" t="n">
         <v>666.6869470197619</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.4</v>
+        <v>-7.36</v>
       </c>
       <c r="L25" t="n">
-        <v>5.03</v>
+        <v>7.95</v>
       </c>
       <c r="M25" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="N25" t="n">
         <v>4.2</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>10.93</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H26" t="n">
-        <v>646.9</v>
+        <v>631.6</v>
       </c>
       <c r="I26" t="n">
         <v>637.4570405134573</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.33</v>
+        <v>-6.59</v>
       </c>
       <c r="L26" t="n">
         <v>9.77</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.34</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43538</v>
+        <v>43539</v>
       </c>
       <c r="H27" t="n">
-        <v>631.1</v>
+        <v>641.55</v>
       </c>
       <c r="I27" t="n">
         <v>640.1112366403647</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K27" t="n">
-        <v>0.08</v>
+        <v>-1.58</v>
       </c>
       <c r="L27" t="n">
         <v>5.29</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>8.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H28" t="n">
-        <v>634.85</v>
+        <v>603.7</v>
       </c>
       <c r="I28" t="n">
         <v>608.7055119920656</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.04</v>
+        <v>-5.9</v>
       </c>
       <c r="L28" t="n">
-        <v>3.9</v>
+        <v>7.08</v>
       </c>
       <c r="M28" t="n">
         <v>1.67</v>
       </c>
       <c r="N28" t="n">
-        <v>2.04</v>
+        <v>4.91</v>
       </c>
       <c r="O28" t="n">
         <v>1.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.98</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43784</v>
+        <v>43787</v>
       </c>
       <c r="H29" t="n">
-        <v>301</v>
+        <v>365.55</v>
       </c>
       <c r="I29" t="n">
         <v>314.8250526878436</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K29" t="n">
-        <v>50.14</v>
+        <v>39.45</v>
       </c>
       <c r="L29" t="n">
         <v>5.42</v>
@@ -2094,7 +2441,7 @@
         <v>5.58</v>
       </c>
       <c r="N29" t="n">
-        <v>6.72</v>
+        <v>21.45</v>
       </c>
       <c r="O29" t="n">
         <v>-4.91</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>22.96</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H30" t="n">
-        <v>335.6</v>
+        <v>319.9</v>
       </c>
       <c r="I30" t="n">
         <v>328.8924569500089</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K30" t="n">
-        <v>-8.19</v>
+        <v>-12.49</v>
       </c>
       <c r="L30" t="n">
         <v>15.09</v>
@@ -2151,7 +2510,7 @@
         <v>0.93</v>
       </c>
       <c r="N30" t="n">
-        <v>4.12</v>
+        <v>4.68</v>
       </c>
       <c r="O30" t="n">
         <v>21.45</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.36</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43930</v>
+        <v>43934</v>
       </c>
       <c r="H31" t="n">
-        <v>247.65</v>
+        <v>299.1</v>
       </c>
       <c r="I31" t="n">
         <v>257.1989959492208</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K31" t="n">
-        <v>22.59</v>
+        <v>6.5</v>
       </c>
       <c r="L31" t="n">
         <v>8.300000000000001</v>
@@ -2208,7 +2579,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>8.69</v>
+        <v>20.78</v>
       </c>
       <c r="O31" t="n">
         <v>-4.68</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>29.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44018</v>
+        <v>44019</v>
       </c>
       <c r="H32" t="n">
-        <v>428</v>
+        <v>416.5</v>
       </c>
       <c r="I32" t="n">
         <v>419.7419324225363</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K32" t="n">
-        <v>43.1</v>
+        <v>39.25</v>
       </c>
       <c r="L32" t="n">
         <v>15.41</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>18.29</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44050</v>
+        <v>44053</v>
       </c>
       <c r="H33" t="n">
-        <v>453.45</v>
+        <v>471.3</v>
       </c>
       <c r="I33" t="n">
         <v>468.5194145821204</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.869999999999999</v>
+        <v>-13.16</v>
       </c>
       <c r="L33" t="n">
-        <v>12.1</v>
+        <v>14.44</v>
       </c>
       <c r="M33" t="n">
         <v>2.49</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H34" t="n">
-        <v>516.25</v>
+        <v>488.55</v>
       </c>
       <c r="I34" t="n">
         <v>489.1627816137536</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K34" t="n">
-        <v>9.539999999999999</v>
+        <v>3.66</v>
       </c>
       <c r="L34" t="n">
         <v>6.28</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44291</v>
+        <v>44292</v>
       </c>
       <c r="H35" t="n">
-        <v>479.05</v>
+        <v>507.65</v>
       </c>
       <c r="I35" t="n">
         <v>498.1307454083875</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K35" t="n">
-        <v>1.94</v>
+        <v>-3.91</v>
       </c>
       <c r="L35" t="n">
         <v>8.890000000000001</v>
@@ -2436,7 +2855,7 @@
         <v>1.17</v>
       </c>
       <c r="N35" t="n">
-        <v>4.09</v>
+        <v>5.97</v>
       </c>
       <c r="O35" t="n">
         <v>-5.37</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.95</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44400</v>
+        <v>44403</v>
       </c>
       <c r="H36" t="n">
-        <v>649.9</v>
+        <v>626.4</v>
       </c>
       <c r="I36" t="n">
         <v>630.2864465674513</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K36" t="n">
-        <v>28.02</v>
+        <v>23.39</v>
       </c>
       <c r="L36" t="n">
         <v>5.55</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.15</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44512</v>
+        <v>44515</v>
       </c>
       <c r="H37" t="n">
-        <v>523.8</v>
+        <v>535.75</v>
       </c>
       <c r="I37" t="n">
         <v>532.7774372484878</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K37" t="n">
-        <v>16.38</v>
+        <v>14.47</v>
       </c>
       <c r="L37" t="n">
         <v>3.78</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.98</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H38" t="n">
-        <v>501.4</v>
+        <v>482.6</v>
       </c>
       <c r="I38" t="n">
         <v>487.6291202294165</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.41</v>
+        <v>-9.92</v>
       </c>
       <c r="L38" t="n">
-        <v>6.86</v>
+        <v>10.25</v>
       </c>
       <c r="M38" t="n">
         <v>0.09</v>
       </c>
       <c r="N38" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
         <v>2.28</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.48</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44524</v>
+        <v>44525</v>
       </c>
       <c r="H39" t="n">
-        <v>519.75</v>
+        <v>529.3</v>
       </c>
       <c r="I39" t="n">
         <v>525.7332267174799</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.7</v>
+        <v>-9.68</v>
       </c>
       <c r="L39" t="n">
-        <v>9.289999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="M39" t="n">
         <v>0.52</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.12</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H40" t="n">
-        <v>497.35</v>
+        <v>482.95</v>
       </c>
       <c r="I40" t="n">
         <v>484.4590770760377</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.04</v>
+        <v>-8.76</v>
       </c>
       <c r="L40" t="n">
         <v>10.73</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>10.16</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H41" t="n">
-        <v>477.1</v>
+        <v>479.15</v>
       </c>
       <c r="I41" t="n">
         <v>478.4893317588759</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K41" t="n">
-        <v>1.21</v>
+        <v>0.79</v>
       </c>
       <c r="L41" t="n">
         <v>4.67</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.49</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44673</v>
+        <v>44676</v>
       </c>
       <c r="H42" t="n">
-        <v>443.55</v>
+        <v>427.05</v>
       </c>
       <c r="I42" t="n">
         <v>441.8863578319006</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.43</v>
+        <v>-10.87</v>
       </c>
       <c r="L42" t="n">
-        <v>7.71</v>
+        <v>11.2</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1</v>
+        <v>0.74</v>
       </c>
       <c r="N42" t="n">
-        <v>2.22</v>
+        <v>3.72</v>
       </c>
       <c r="O42" t="n">
         <v>0.43</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.66</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44789</v>
+        <v>44790</v>
       </c>
       <c r="H43" t="n">
-        <v>389.25</v>
+        <v>403.35</v>
       </c>
       <c r="I43" t="n">
         <v>399.9225814797509</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K43" t="n">
-        <v>8.85</v>
+        <v>5.55</v>
       </c>
       <c r="L43" t="n">
         <v>6.17</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.11</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="H44" t="n">
-        <v>413.1</v>
+        <v>398.85</v>
       </c>
       <c r="I44" t="n">
         <v>403.5578059391565</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K44" t="n">
-        <v>2.42</v>
+        <v>-1.12</v>
       </c>
       <c r="L44" t="n">
         <v>10.4</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.57</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44967</v>
+        <v>44970</v>
       </c>
       <c r="H45" t="n">
-        <v>400.4</v>
+        <v>422.6</v>
       </c>
       <c r="I45" t="n">
         <v>412.4529177779336</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.39</v>
+        <v>-5.95</v>
       </c>
       <c r="L45" t="n">
-        <v>3.81</v>
+        <v>6.24</v>
       </c>
       <c r="M45" t="n">
-        <v>1.01</v>
+        <v>3.57</v>
       </c>
       <c r="N45" t="n">
-        <v>3.46</v>
+        <v>5.54</v>
       </c>
       <c r="O45" t="n">
         <v>-3.45</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.52</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45159</v>
+        <v>45160</v>
       </c>
       <c r="H46" t="n">
-        <v>775.05</v>
+        <v>759</v>
       </c>
       <c r="I46" t="n">
         <v>760.8887140325257</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K46" t="n">
-        <v>83.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="L46" t="n">
         <v>4.33</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7</v>
+      </c>
+      <c r="U46" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>10.36</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45177</v>
+        <v>45180</v>
       </c>
       <c r="H47" t="n">
-        <v>776.85</v>
+        <v>810.95</v>
       </c>
       <c r="I47" t="n">
         <v>808.1914508801431</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.35</v>
+        <v>-6.84</v>
       </c>
       <c r="L47" t="n">
-        <v>6.06</v>
+        <v>7.14</v>
       </c>
       <c r="M47" t="n">
         <v>0.92</v>
       </c>
       <c r="N47" t="n">
-        <v>3.97</v>
+        <v>4.39</v>
       </c>
       <c r="O47" t="n">
         <v>-2.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.34</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45191</v>
+        <v>45194</v>
       </c>
       <c r="H48" t="n">
-        <v>802.8</v>
+        <v>785.55</v>
       </c>
       <c r="I48" t="n">
         <v>787.203246710557</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-1</v>
+        <v>-3.13</v>
       </c>
       <c r="L48" t="n">
         <v>4.43</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.91</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="H49" t="n">
-        <v>779.05</v>
+        <v>806.5</v>
       </c>
       <c r="I49" t="n">
         <v>805.5335676604939</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K49" t="n">
-        <v>0.83</v>
+        <v>-2.67</v>
       </c>
       <c r="L49" t="n">
         <v>9.69</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.35</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45335</v>
+        <v>45336</v>
       </c>
       <c r="H50" t="n">
-        <v>832.2</v>
+        <v>797.2</v>
       </c>
       <c r="I50" t="n">
         <v>831.0947295269838</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K50" t="n">
-        <v>3.19</v>
+        <v>-1.15</v>
       </c>
       <c r="L50" t="n">
         <v>4.13</v>
@@ -3291,7 +3890,7 @@
         <v>1.12</v>
       </c>
       <c r="N50" t="n">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="O50" t="n">
         <v>3.52</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.85</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="H51" t="n">
-        <v>862.55</v>
+        <v>894.15</v>
       </c>
       <c r="I51" t="n">
         <v>891.6953701269549</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.16</v>
       </c>
       <c r="L51" t="n">
-        <v>11.77</v>
+        <v>13.52</v>
       </c>
       <c r="M51" t="n">
         <v>1.45</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>13.45</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H52" t="n">
-        <v>1649.8</v>
+        <v>1636.75</v>
       </c>
       <c r="I52" t="n">
         <v>1638.465666865761</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K52" t="n">
-        <v>84.51000000000001</v>
+        <v>83.05</v>
       </c>
       <c r="L52" t="n">
         <v>3.01</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.83</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45573</v>
+        <v>45574</v>
       </c>
       <c r="H53" t="n">
-        <v>1734.55</v>
+        <v>1786.15</v>
       </c>
       <c r="I53" t="n">
         <v>1781.274853469374</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>-5.98</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>7.77</v>
+        <v>9.67</v>
       </c>
       <c r="M53" t="n">
         <v>4.17</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H54" t="n">
-        <v>1674.55</v>
+        <v>1663.8</v>
       </c>
       <c r="I54" t="n">
         <v>1669.295494963951</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.25</v>
+        <v>-6.85</v>
       </c>
       <c r="L54" t="n">
-        <v>7.55</v>
+        <v>7.68</v>
       </c>
       <c r="M54" t="n">
         <v>0.67</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H55" t="n">
-        <v>1614.5</v>
+        <v>1639.35</v>
       </c>
       <c r="I55" t="n">
         <v>1634.097827820482</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K55" t="n">
-        <v>2.96</v>
+        <v>1.47</v>
       </c>
       <c r="L55" t="n">
         <v>6.79</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>8.75</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H56" t="n">
-        <v>1541.7</v>
+        <v>1496.9</v>
       </c>
       <c r="I56" t="n">
         <v>1520.541781136339</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.96</v>
+        <v>-8.69</v>
       </c>
       <c r="L56" t="n">
-        <v>6.17</v>
+        <v>8.99</v>
       </c>
       <c r="M56" t="n">
-        <v>0.5</v>
+        <v>1.08</v>
       </c>
       <c r="N56" t="n">
         <v>3.24</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.37</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H57" t="n">
-        <v>1429.6</v>
+        <v>1456.35</v>
       </c>
       <c r="I57" t="n">
         <v>1453.110220363553</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K57" t="n">
-        <v>4.5</v>
+        <v>2.71</v>
       </c>
       <c r="L57" t="n">
         <v>3.77</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45755</v>
+        <v>45756</v>
       </c>
       <c r="H58" t="n">
-        <v>1440.8</v>
+        <v>1376.3</v>
       </c>
       <c r="I58" t="n">
         <v>1414.730028538929</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.07</v>
+        <v>-5.5</v>
       </c>
       <c r="L58" t="n">
-        <v>6.62</v>
+        <v>8</v>
       </c>
       <c r="M58" t="n">
         <v>9.32</v>
       </c>
       <c r="N58" t="n">
-        <v>3.84</v>
+        <v>4.48</v>
       </c>
       <c r="O58" t="n">
         <v>1.87</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>14.1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="H59" t="n">
-        <v>1497.5</v>
+        <v>1514</v>
       </c>
       <c r="I59" t="n">
         <v>1511.080731690727</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.81</v>
+        <v>-10.01</v>
       </c>
       <c r="L59" t="n">
-        <v>9.17</v>
+        <v>11.02</v>
       </c>
       <c r="M59" t="n">
         <v>2.67</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.66</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="H60" t="n">
-        <v>2044.6</v>
+        <v>1973.9</v>
       </c>
       <c r="I60" t="n">
         <v>1995.104768079459</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K60" t="n">
-        <v>35.05</v>
+        <v>30.38</v>
       </c>
       <c r="L60" t="n">
         <v>2.69</v>
@@ -3861,7 +4580,7 @@
         <v>2.11</v>
       </c>
       <c r="N60" t="n">
-        <v>3.11</v>
+        <v>3.46</v>
       </c>
       <c r="O60" t="n">
         <v>1.1</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="H61" t="n">
-        <v>2051.9</v>
+        <v>2116.3</v>
       </c>
       <c r="I61" t="n">
         <v>2055.813439556279</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K61" t="n">
-        <v>-3.95</v>
+        <v>-7.21</v>
       </c>
       <c r="L61" t="n">
-        <v>5.17</v>
+        <v>7.4</v>
       </c>
       <c r="M61" t="n">
         <v>1.03</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H62" t="n">
-        <v>2030.7</v>
+        <v>1971.7</v>
       </c>
       <c r="I62" t="n">
         <v>1989.846015563035</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.04</v>
+        <v>-6.83</v>
       </c>
       <c r="L62" t="n">
-        <v>5.3</v>
+        <v>7.54</v>
       </c>
       <c r="M62" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="N62" t="n">
         <v>3.23</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.93</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="H63" t="n">
-        <v>1921.3</v>
+        <v>1944</v>
       </c>
       <c r="I63" t="n">
         <v>1942.260443527758</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K63" t="n">
-        <v>2.56</v>
+        <v>1.4</v>
       </c>
       <c r="L63" t="n">
         <v>2.04</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H64" t="n">
-        <v>1989.8</v>
+        <v>1935</v>
       </c>
       <c r="I64" t="n">
         <v>1975.167357933535</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K64" t="n">
-        <v>2.36</v>
+        <v>-0.46</v>
       </c>
       <c r="L64" t="n">
         <v>2.64</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>8.76</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H65" t="n">
-        <v>2058.6</v>
+        <v>2085</v>
       </c>
       <c r="I65" t="n">
         <v>2081.363271258752</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.39</v>
+        <v>-7.75</v>
       </c>
       <c r="L65" t="n">
-        <v>7.42</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M65" t="n">
         <v>3.88</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.37</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H66" t="n">
-        <v>2274.9</v>
+        <v>2201.2</v>
       </c>
       <c r="I66" t="n">
         <v>2222.360623951688</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K66" t="n">
-        <v>9.109999999999999</v>
+        <v>5.57</v>
       </c>
       <c r="L66" t="n">
         <v>5.68</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>13.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H67" t="n">
-        <v>2317.9</v>
+        <v>2390.7</v>
       </c>
       <c r="I67" t="n">
         <v>2340.765748580192</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.3</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M67" t="n">
         <v>1.27</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="H68" t="n">
-        <v>2331</v>
+        <v>2295</v>
       </c>
       <c r="I68" t="n">
         <v>2306.245245646656</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.5</v>
+        <v>-4</v>
       </c>
       <c r="L68" t="n">
-        <v>4.66</v>
+        <v>4.9</v>
       </c>
       <c r="M68" t="n">
         <v>2.07</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>17</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9335,7 +10170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.3</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="6">
@@ -9345,7 +10180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9355,7 +10190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
@@ -9365,7 +10200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9375,7 +10210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -9385,7 +10220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.8</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="11">
@@ -9395,7 +10230,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9405,7 +10240,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9415,7 +10250,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.9</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="14">
@@ -9425,7 +10260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.92</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="15">
@@ -9435,7 +10270,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.83</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="16">
@@ -9445,7 +10280,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.92</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="17">
@@ -9455,7 +10290,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84.51000000000001</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="18">
@@ -9465,7 +10300,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.7</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="19">
@@ -9475,7 +10310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.08</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="20">
@@ -9485,7 +10320,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.55</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="21">
@@ -9495,7 +10330,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.41</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="22">
@@ -9505,7 +10340,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9515,7 +10350,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -9525,7 +10360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
@@ -9545,7 +10380,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.37</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="27">
@@ -9555,7 +10390,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.11</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="28">
@@ -9565,7 +10400,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
